--- a/athletes/A005/activity_overrides.xlsx
+++ b/athletes/A005/activity_overrides.xlsx
@@ -466,7 +466,7 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="54" customWidth="1" min="17" max="17"/>
-    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,62 +778,58 @@
       <c r="R5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>59049333.fit</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2013-05-11</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Parkrun Highbury Fields</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="3" t="n">
         <v>4.81</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 83%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 83%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 83%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2348,62 +2344,58 @@
       <c r="R34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>117082650.fit</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="n">
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>2014-01-18</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>Highbury Fields Parkrun 5k</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="3" t="n">
         <v>4.85</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="M35" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="O35" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 88%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -3000,62 +2992,58 @@
       <c r="R46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>198113469.fit</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="4" t="n">
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>2014-08-14</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>Warm up for Midnattsloppet - 5k around Sodernas</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="L47" s="3" t="n">
         <v>5.01</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="M47" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="O47" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>Named race but easy HR 91%LTHR — DNS/jogged?</t>
-        </is>
-      </c>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Named race but easy HR 91%LTHR — DNS/jogged?</t>
-        </is>
-      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>Named race but HR 91%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3664,62 +3652,58 @@
       <c r="R58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>262980058.fit</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="4" t="n">
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+      <c r="I59" s="3" t="n"/>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>2014-12-25</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>Highbury Fields Xmas Parkrun</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="3" t="n">
         <v>4.82</v>
       </c>
-      <c r="M59" s="4" t="n">
+      <c r="M59" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="N59" s="4" t="n">
+      <c r="N59" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="O59" s="4" t="n">
+      <c r="O59" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R59" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 92%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -7576,62 +7560,58 @@
       <c r="R130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>614247010.fit</t>
         </is>
       </c>
-      <c r="B131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="4" t="n">
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
         <v>15.534</v>
       </c>
-      <c r="E131" s="4" t="n"/>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="4" t="n"/>
-      <c r="H131" s="4" t="n"/>
-      <c r="I131" s="4" t="n"/>
-      <c r="J131" s="4" t="inlineStr">
+      <c r="E131" s="3" t="n"/>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="n"/>
+      <c r="I131" s="3" t="n"/>
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>2016-04-30</t>
         </is>
       </c>
-      <c r="K131" s="4" t="inlineStr">
+      <c r="K131" s="3" t="inlineStr">
         <is>
           <t>Marathon effort dans la Paris</t>
         </is>
       </c>
-      <c r="L131" s="4" t="n">
+      <c r="L131" s="3" t="n">
         <v>16.16</v>
       </c>
-      <c r="M131" s="4" t="n">
+      <c r="M131" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="N131" s="4" t="n">
+      <c r="N131" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="O131" s="4" t="n">
+      <c r="O131" s="3" t="n">
         <v>75.2</v>
       </c>
-      <c r="P131" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R131" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 88%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -8295,7 +8275,7 @@
         <v>0</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" s="3" t="n">
         <v>5</v>
@@ -8340,62 +8320,58 @@
       <c r="R144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>732270871.fit</t>
         </is>
       </c>
-      <c r="B145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="4" t="n">
+      <c r="B145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E145" s="4" t="n"/>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n"/>
-      <c r="I145" s="4" t="n"/>
-      <c r="J145" s="4" t="inlineStr">
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>2016-08-04</t>
         </is>
       </c>
-      <c r="K145" s="4" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>Sandö and back with fast second 5k. Undulating so ideal practice for Midnattsloppet....</t>
         </is>
       </c>
-      <c r="L145" s="4" t="n">
+      <c r="L145" s="3" t="n">
         <v>10.19</v>
       </c>
-      <c r="M145" s="4" t="n">
+      <c r="M145" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="N145" s="4" t="n">
+      <c r="N145" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="O145" s="4" t="n">
+      <c r="O145" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="P145" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q145" s="4" t="inlineStr">
-        <is>
-          <t>Named race but easy HR 88%LTHR — DNS/jogged?</t>
-        </is>
-      </c>
-      <c r="R145" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Named race but easy HR 88%LTHR — DNS/jogged?</t>
-        </is>
-      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q145" s="3" t="inlineStr">
+        <is>
+          <t>Named race but HR 88%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -11770,62 +11746,58 @@
       <c r="R207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="4" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
         <is>
           <t>1293836200.fit</t>
         </is>
       </c>
-      <c r="B208" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C208" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D208" s="4" t="n">
+      <c r="B208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" s="3" t="n">
         <v>15.534</v>
       </c>
-      <c r="E208" s="4" t="n"/>
-      <c r="F208" s="4" t="n"/>
-      <c r="G208" s="4" t="n"/>
-      <c r="H208" s="4" t="n"/>
-      <c r="I208" s="4" t="n"/>
-      <c r="J208" s="4" t="inlineStr">
+      <c r="E208" s="3" t="n"/>
+      <c r="F208" s="3" t="n"/>
+      <c r="G208" s="3" t="n"/>
+      <c r="H208" s="3" t="n"/>
+      <c r="I208" s="3" t="n"/>
+      <c r="J208" s="3" t="inlineStr">
         <is>
           <t>2017-09-17</t>
         </is>
       </c>
-      <c r="K208" s="4" t="inlineStr">
+      <c r="K208" s="3" t="inlineStr">
         <is>
           <t>10 miler with race effort on hilly bits around 3-12km</t>
         </is>
       </c>
-      <c r="L208" s="4" t="n">
+      <c r="L208" s="3" t="n">
         <v>16.11</v>
       </c>
-      <c r="M208" s="4" t="n">
+      <c r="M208" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="N208" s="4" t="n">
+      <c r="N208" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="O208" s="4" t="n">
+      <c r="O208" s="3" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="P208" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 85%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R208" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 85%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P208" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q208" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 85%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -12696,66 +12668,62 @@
       <c r="R224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
+      <c r="A225" s="3" t="inlineStr">
         <is>
           <t>1422978609.fit</t>
         </is>
       </c>
-      <c r="B225" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" s="4" t="n">
+      <c r="B225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E225" s="4" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>track</t>
         </is>
       </c>
-      <c r="F225" s="4" t="n"/>
-      <c r="G225" s="4" t="n"/>
-      <c r="H225" s="4" t="n"/>
-      <c r="I225" s="4" t="n"/>
-      <c r="J225" s="4" t="inlineStr">
+      <c r="F225" s="3" t="n"/>
+      <c r="G225" s="3" t="n"/>
+      <c r="H225" s="3" t="n"/>
+      <c r="I225" s="3" t="n"/>
+      <c r="J225" s="3" t="inlineStr">
         <is>
           <t>2017-12-16</t>
         </is>
       </c>
-      <c r="K225" s="4" t="inlineStr">
+      <c r="K225" s="3" t="inlineStr">
         <is>
           <t>#Adventrunning Day 16 - 5000m race on an icy track. My first ever track race. A respectable 7th Place in 19’01....</t>
         </is>
       </c>
-      <c r="L225" s="4" t="n">
+      <c r="L225" s="3" t="n">
         <v>5.12</v>
       </c>
-      <c r="M225" s="4" t="n">
+      <c r="M225" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="N225" s="4" t="n">
+      <c r="N225" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="O225" s="4" t="n">
+      <c r="O225" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="P225" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q225" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 90%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R225" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 90%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P225" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q225" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 90%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -16450,62 +16418,58 @@
       <c r="R293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="4" t="inlineStr">
+      <c r="A294" s="3" t="inlineStr">
         <is>
           <t>2028564149.fit</t>
         </is>
       </c>
-      <c r="B294" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C294" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D294" s="4" t="n">
+      <c r="B294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" s="3" t="n">
         <v>15.534</v>
       </c>
-      <c r="E294" s="4" t="n"/>
-      <c r="F294" s="4" t="n"/>
-      <c r="G294" s="4" t="n"/>
-      <c r="H294" s="4" t="n"/>
-      <c r="I294" s="4" t="n"/>
-      <c r="J294" s="4" t="inlineStr">
+      <c r="E294" s="3" t="n"/>
+      <c r="F294" s="3" t="n"/>
+      <c r="G294" s="3" t="n"/>
+      <c r="H294" s="3" t="n"/>
+      <c r="I294" s="3" t="n"/>
+      <c r="J294" s="3" t="inlineStr">
         <is>
           <t>2018-10-09</t>
         </is>
       </c>
-      <c r="K294" s="4" t="inlineStr">
+      <c r="K294" s="3" t="inlineStr">
         <is>
           <t>Dollis Valley Green Walk, then a bit of XC, got lost, and then a stitch - all on a glorious evening!</t>
         </is>
       </c>
-      <c r="L294" s="4" t="n">
+      <c r="L294" s="3" t="n">
         <v>15.64</v>
       </c>
-      <c r="M294" s="4" t="n">
+      <c r="M294" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="N294" s="4" t="n">
+      <c r="N294" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="O294" s="4" t="n">
+      <c r="O294" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="P294" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q294" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 87%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R294" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 87%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P294" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q294" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 87%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -17480,62 +17444,58 @@
       <c r="R312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="4" t="inlineStr">
+      <c r="A313" s="3" t="inlineStr">
         <is>
           <t>2188462196.fit</t>
         </is>
       </c>
-      <c r="B313" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C313" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D313" s="4" t="n">
+      <c r="B313" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C313" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E313" s="4" t="n"/>
-      <c r="F313" s="4" t="n"/>
-      <c r="G313" s="4" t="n"/>
-      <c r="H313" s="4" t="n"/>
-      <c r="I313" s="4" t="n"/>
-      <c r="J313" s="4" t="inlineStr">
+      <c r="E313" s="3" t="n"/>
+      <c r="F313" s="3" t="n"/>
+      <c r="G313" s="3" t="n"/>
+      <c r="H313" s="3" t="n"/>
+      <c r="I313" s="3" t="n"/>
+      <c r="J313" s="3" t="inlineStr">
         <is>
           <t>2019-01-01</t>
         </is>
       </c>
-      <c r="K313" s="4" t="inlineStr">
+      <c r="K313" s="3" t="inlineStr">
         <is>
           <t>Starting 2019 with more Devon coastal path and cross country!!</t>
         </is>
       </c>
-      <c r="L313" s="4" t="n">
+      <c r="L313" s="3" t="n">
         <v>10.73</v>
       </c>
-      <c r="M313" s="4" t="n">
+      <c r="M313" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="N313" s="4" t="n">
+      <c r="N313" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="O313" s="4" t="n">
+      <c r="O313" s="3" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="P313" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q313" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 84%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R313" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 84%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P313" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q313" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 84%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R313" s="3" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -19972,62 +19932,58 @@
       <c r="R358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="4" t="inlineStr">
+      <c r="A359" s="3" t="inlineStr">
         <is>
           <t>2643864556.fit</t>
         </is>
       </c>
-      <c r="B359" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C359" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D359" s="4" t="n">
+      <c r="B359" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C359" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D359" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E359" s="4" t="n"/>
-      <c r="F359" s="4" t="n"/>
-      <c r="G359" s="4" t="n"/>
-      <c r="H359" s="4" t="n"/>
-      <c r="I359" s="4" t="n"/>
-      <c r="J359" s="4" t="inlineStr">
+      <c r="E359" s="3" t="n"/>
+      <c r="F359" s="3" t="n"/>
+      <c r="G359" s="3" t="n"/>
+      <c r="H359" s="3" t="n"/>
+      <c r="I359" s="3" t="n"/>
+      <c r="J359" s="3" t="inlineStr">
         <is>
           <t>2019-06-29</t>
         </is>
       </c>
-      <c r="K359" s="4" t="inlineStr">
+      <c r="K359" s="3" t="inlineStr">
         <is>
           <t>‘Crowd scene’ parkrun at ME then fast last 400m</t>
         </is>
       </c>
-      <c r="L359" s="4" t="n">
+      <c r="L359" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="M359" s="4" t="n">
+      <c r="M359" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="N359" s="4" t="n">
+      <c r="N359" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="O359" s="4" t="n">
+      <c r="O359" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="P359" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q359" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 93%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R359" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 93%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P359" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q359" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 93%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R359" s="3" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -20844,62 +20800,58 @@
       <c r="R374" s="3" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="4" t="inlineStr">
+      <c r="A375" s="3" t="inlineStr">
         <is>
           <t>2890502268.fit</t>
         </is>
       </c>
-      <c r="B375" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C375" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D375" s="4" t="n">
+      <c r="B375" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D375" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E375" s="4" t="n"/>
-      <c r="F375" s="4" t="n"/>
-      <c r="G375" s="4" t="n"/>
-      <c r="H375" s="4" t="n"/>
-      <c r="I375" s="4" t="n"/>
-      <c r="J375" s="4" t="inlineStr">
+      <c r="E375" s="3" t="n"/>
+      <c r="F375" s="3" t="n"/>
+      <c r="G375" s="3" t="n"/>
+      <c r="H375" s="3" t="n"/>
+      <c r="I375" s="3" t="n"/>
+      <c r="J375" s="3" t="inlineStr">
         <is>
           <t>2019-09-21</t>
         </is>
       </c>
-      <c r="K375" s="4" t="inlineStr">
+      <c r="K375" s="3" t="inlineStr">
         <is>
           <t>HF parkrun pacing friend’s 9 year old to 23’15</t>
         </is>
       </c>
-      <c r="L375" s="4" t="n">
+      <c r="L375" s="3" t="n">
         <v>5.13</v>
       </c>
-      <c r="M375" s="4" t="n">
+      <c r="M375" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="N375" s="4" t="n">
+      <c r="N375" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="O375" s="4" t="n">
+      <c r="O375" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="P375" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q375" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 89%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R375" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 89%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P375" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q375" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 89%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R375" s="3" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -22630,62 +22582,58 @@
       <c r="R407" s="3" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>3469394900.fit</t>
         </is>
       </c>
-      <c r="B408" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C408" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D408" s="4" t="n">
+      <c r="B408" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D408" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E408" s="4" t="n"/>
-      <c r="F408" s="4" t="n"/>
-      <c r="G408" s="4" t="n"/>
-      <c r="H408" s="4" t="n"/>
-      <c r="I408" s="4" t="n"/>
-      <c r="J408" s="4" t="inlineStr">
+      <c r="E408" s="3" t="n"/>
+      <c r="F408" s="3" t="n"/>
+      <c r="G408" s="3" t="n"/>
+      <c r="H408" s="3" t="n"/>
+      <c r="I408" s="3" t="n"/>
+      <c r="J408" s="3" t="inlineStr">
         <is>
           <t>2020-04-02</t>
         </is>
       </c>
-      <c r="K408" s="4" t="inlineStr">
+      <c r="K408" s="3" t="inlineStr">
         <is>
           <t>45’ at sub 3 marathon effort</t>
         </is>
       </c>
-      <c r="L408" s="4" t="n">
+      <c r="L408" s="3" t="n">
         <v>10.63</v>
       </c>
-      <c r="M408" s="4" t="n">
+      <c r="M408" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="N408" s="4" t="n">
+      <c r="N408" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="O408" s="4" t="n">
+      <c r="O408" s="3" t="n">
         <v>45.4</v>
       </c>
-      <c r="P408" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q408" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R408" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P408" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q408" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 92%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R408" s="3" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -22962,62 +22910,58 @@
       <c r="R413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="4" t="inlineStr">
+      <c r="A414" s="3" t="inlineStr">
         <is>
           <t>3729544672.fit</t>
         </is>
       </c>
-      <c r="B414" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C414" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D414" s="4" t="n">
+      <c r="B414" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C414" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D414" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E414" s="4" t="n"/>
-      <c r="F414" s="4" t="n"/>
-      <c r="G414" s="4" t="n"/>
-      <c r="H414" s="4" t="n"/>
-      <c r="I414" s="4" t="n"/>
-      <c r="J414" s="4" t="inlineStr">
+      <c r="E414" s="3" t="n"/>
+      <c r="F414" s="3" t="n"/>
+      <c r="G414" s="3" t="n"/>
+      <c r="H414" s="3" t="n"/>
+      <c r="I414" s="3" t="n"/>
+      <c r="J414" s="3" t="inlineStr">
         <is>
           <t>2020-05-22</t>
         </is>
       </c>
-      <c r="K414" s="4" t="inlineStr">
+      <c r="K414" s="3" t="inlineStr">
         <is>
           <t>Trudge back from TT with burning lungs and residual lactic legs</t>
         </is>
       </c>
-      <c r="L414" s="4" t="n">
+      <c r="L414" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M414" s="4" t="n">
+      <c r="M414" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="N414" s="4" t="n">
+      <c r="N414" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="O414" s="4" t="n">
+      <c r="O414" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="P414" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q414" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 84%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R414" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 84%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P414" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q414" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 84%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R414" s="3" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
@@ -25956,62 +25900,58 @@
       <c r="R468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="4" t="inlineStr">
+      <c r="A469" s="3" t="inlineStr">
         <is>
           <t>6371261009.fit</t>
         </is>
       </c>
-      <c r="B469" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C469" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D469" s="4" t="n">
+      <c r="B469" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C469" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D469" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E469" s="4" t="n"/>
-      <c r="F469" s="4" t="n"/>
-      <c r="G469" s="4" t="n"/>
-      <c r="H469" s="4" t="n"/>
-      <c r="I469" s="4" t="n"/>
-      <c r="J469" s="4" t="inlineStr">
+      <c r="E469" s="3" t="n"/>
+      <c r="F469" s="3" t="n"/>
+      <c r="G469" s="3" t="n"/>
+      <c r="H469" s="3" t="n"/>
+      <c r="I469" s="3" t="n"/>
+      <c r="J469" s="3" t="inlineStr">
         <is>
           <t>2021-09-21</t>
         </is>
       </c>
-      <c r="K469" s="4" t="inlineStr">
+      <c r="K469" s="3" t="inlineStr">
         <is>
           <t>5k @ around Stryd suggested W for Saturday’s race</t>
         </is>
       </c>
-      <c r="L469" s="4" t="n">
+      <c r="L469" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M469" s="4" t="n">
+      <c r="M469" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="N469" s="4" t="n">
+      <c r="N469" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="O469" s="4" t="n">
+      <c r="O469" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="P469" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q469" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 91%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R469" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 91%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P469" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q469" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 91%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -27364,62 +27304,58 @@
       <c r="R494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="4" t="inlineStr">
+      <c r="A495" s="3" t="inlineStr">
         <is>
           <t>7148070714.fit</t>
         </is>
       </c>
-      <c r="B495" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C495" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D495" s="4" t="n">
+      <c r="B495" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C495" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D495" s="3" t="n">
         <v>21.097</v>
       </c>
-      <c r="E495" s="4" t="n"/>
-      <c r="F495" s="4" t="n"/>
-      <c r="G495" s="4" t="n"/>
-      <c r="H495" s="4" t="n"/>
-      <c r="I495" s="4" t="n"/>
-      <c r="J495" s="4" t="inlineStr">
+      <c r="E495" s="3" t="n"/>
+      <c r="F495" s="3" t="n"/>
+      <c r="G495" s="3" t="n"/>
+      <c r="H495" s="3" t="n"/>
+      <c r="I495" s="3" t="n"/>
+      <c r="J495" s="3" t="inlineStr">
         <is>
           <t>2022-02-22</t>
         </is>
       </c>
-      <c r="K495" s="4" t="inlineStr">
+      <c r="K495" s="3" t="inlineStr">
         <is>
           <t>Lunchtime Half</t>
         </is>
       </c>
-      <c r="L495" s="4" t="n">
+      <c r="L495" s="3" t="n">
         <v>21.14</v>
       </c>
-      <c r="M495" s="4" t="n">
+      <c r="M495" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="N495" s="4" t="n">
+      <c r="N495" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="O495" s="4" t="n">
+      <c r="O495" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="P495" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q495" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 83%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R495" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 83%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P495" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q495" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 83%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R495" s="3" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -34420,62 +34356,58 @@
       <c r="R624" s="3" t="inlineStr"/>
     </row>
     <row r="625">
-      <c r="A625" s="4" t="inlineStr">
+      <c r="A625" s="3" t="inlineStr">
         <is>
           <t>11727631106.fit</t>
         </is>
       </c>
-      <c r="B625" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C625" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D625" s="4" t="n">
+      <c r="B625" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C625" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D625" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E625" s="4" t="n"/>
-      <c r="F625" s="4" t="n"/>
-      <c r="G625" s="4" t="n"/>
-      <c r="H625" s="4" t="n"/>
-      <c r="I625" s="4" t="n"/>
-      <c r="J625" s="4" t="inlineStr">
+      <c r="E625" s="3" t="n"/>
+      <c r="F625" s="3" t="n"/>
+      <c r="G625" s="3" t="n"/>
+      <c r="H625" s="3" t="n"/>
+      <c r="I625" s="3" t="n"/>
+      <c r="J625" s="3" t="inlineStr">
         <is>
           <t>2024-03-16</t>
         </is>
       </c>
-      <c r="K625" s="4" t="inlineStr">
+      <c r="K625" s="3" t="inlineStr">
         <is>
           <t>Haga parkrun Z3</t>
         </is>
       </c>
-      <c r="L625" s="4" t="n">
+      <c r="L625" s="3" t="n">
         <v>5.05</v>
       </c>
-      <c r="M625" s="4" t="n">
+      <c r="M625" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="N625" s="4" t="n">
+      <c r="N625" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="O625" s="4" t="n">
+      <c r="O625" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="P625" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q625" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 93%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R625" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 93%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P625" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q625" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 93%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R625" s="3" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="3" t="inlineStr">
@@ -36048,62 +35980,58 @@
       <c r="R654" s="3" t="inlineStr"/>
     </row>
     <row r="655">
-      <c r="A655" s="4" t="inlineStr">
+      <c r="A655" s="3" t="inlineStr">
         <is>
           <t>13349648272.fit</t>
         </is>
       </c>
-      <c r="B655" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C655" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D655" s="4" t="n">
+      <c r="B655" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C655" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D655" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E655" s="4" t="n"/>
-      <c r="F655" s="4" t="n"/>
-      <c r="G655" s="4" t="n"/>
-      <c r="H655" s="4" t="n"/>
-      <c r="I655" s="4" t="n"/>
-      <c r="J655" s="4" t="inlineStr">
+      <c r="E655" s="3" t="n"/>
+      <c r="F655" s="3" t="n"/>
+      <c r="G655" s="3" t="n"/>
+      <c r="H655" s="3" t="n"/>
+      <c r="I655" s="3" t="n"/>
+      <c r="J655" s="3" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="K655" s="4" t="inlineStr">
+      <c r="K655" s="3" t="inlineStr">
         <is>
           <t>Judarskogen parkrun premiär</t>
         </is>
       </c>
-      <c r="L655" s="4" t="n">
+      <c r="L655" s="3" t="n">
         <v>5.01</v>
       </c>
-      <c r="M655" s="4" t="n">
+      <c r="M655" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="N655" s="4" t="n">
+      <c r="N655" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="O655" s="4" t="n">
+      <c r="O655" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="P655" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q655" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R655" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 88%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P655" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q655" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 88%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R655" s="3" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -36268,62 +36196,58 @@
       <c r="R658" s="3" t="inlineStr"/>
     </row>
     <row r="659">
-      <c r="A659" s="4" t="inlineStr">
+      <c r="A659" s="3" t="inlineStr">
         <is>
           <t>13709829308.fit</t>
         </is>
       </c>
-      <c r="B659" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C659" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D659" s="4" t="n">
+      <c r="B659" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C659" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D659" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E659" s="4" t="n"/>
-      <c r="F659" s="4" t="n"/>
-      <c r="G659" s="4" t="n"/>
-      <c r="H659" s="4" t="n"/>
-      <c r="I659" s="4" t="n"/>
-      <c r="J659" s="4" t="inlineStr">
+      <c r="E659" s="3" t="n"/>
+      <c r="F659" s="3" t="n"/>
+      <c r="G659" s="3" t="n"/>
+      <c r="H659" s="3" t="n"/>
+      <c r="I659" s="3" t="n"/>
+      <c r="J659" s="3" t="inlineStr">
         <is>
           <t>2024-11-09</t>
         </is>
       </c>
-      <c r="K659" s="4" t="inlineStr">
+      <c r="K659" s="3" t="inlineStr">
         <is>
           <t>Judarskogen parkrun</t>
         </is>
       </c>
-      <c r="L659" s="4" t="n">
+      <c r="L659" s="3" t="n">
         <v>5.01</v>
       </c>
-      <c r="M659" s="4" t="n">
+      <c r="M659" s="3" t="n">
         <v>163</v>
       </c>
-      <c r="N659" s="4" t="n">
+      <c r="N659" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="O659" s="4" t="n">
+      <c r="O659" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="P659" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q659" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R659" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 92%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P659" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q659" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 92%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R659" s="3" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="3" t="inlineStr">
@@ -38303,7 +38227,7 @@
         <v>0</v>
       </c>
       <c r="C696" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D696" s="3" t="n">
         <v>5</v>
@@ -40790,62 +40714,58 @@
       <c r="R741" s="2" t="inlineStr"/>
     </row>
     <row r="742">
-      <c r="A742" s="4" t="inlineStr">
+      <c r="A742" s="3" t="inlineStr">
         <is>
           <t>18035730815.fit</t>
         </is>
       </c>
-      <c r="B742" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C742" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D742" s="4" t="n">
+      <c r="B742" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C742" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D742" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E742" s="4" t="n"/>
-      <c r="F742" s="4" t="n"/>
-      <c r="G742" s="4" t="n"/>
-      <c r="H742" s="4" t="n"/>
-      <c r="I742" s="4" t="n"/>
-      <c r="J742" s="4" t="inlineStr">
+      <c r="E742" s="3" t="n"/>
+      <c r="F742" s="3" t="n"/>
+      <c r="G742" s="3" t="n"/>
+      <c r="H742" s="3" t="n"/>
+      <c r="I742" s="3" t="n"/>
+      <c r="J742" s="3" t="inlineStr">
         <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="K742" s="4" t="inlineStr">
+      <c r="K742" s="3" t="inlineStr">
         <is>
           <t>Glorious winter 10k around Djurgården</t>
         </is>
       </c>
-      <c r="L742" s="4" t="n">
+      <c r="L742" s="3" t="n">
         <v>10.03</v>
       </c>
-      <c r="M742" s="4" t="n">
+      <c r="M742" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="N742" s="4" t="n">
+      <c r="N742" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="O742" s="4" t="n">
+      <c r="O742" s="3" t="n">
         <v>52.7</v>
       </c>
-      <c r="P742" s="4" t="inlineStr">
-        <is>
-          <t>race (low)</t>
-        </is>
-      </c>
-      <c r="Q742" s="4" t="inlineStr">
-        <is>
-          <t>Race keyword but HR 82%LTHR — easy effort</t>
-        </is>
-      </c>
-      <c r="R742" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW: Race keyword but HR 82%LTHR — easy effort</t>
-        </is>
-      </c>
+      <c r="P742" s="3" t="inlineStr">
+        <is>
+          <t>training (medium)</t>
+        </is>
+      </c>
+      <c r="Q742" s="3" t="inlineStr">
+        <is>
+          <t>Race keyword but HR 82%LTHR below race threshold</t>
+        </is>
+      </c>
+      <c r="R742" s="3" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" s="3" t="inlineStr">
